--- a/lab-standards/BGMEA-lab-standard.xlsx
+++ b/lab-standards/BGMEA-lab-standard.xlsx
@@ -567,6 +567,10 @@
           <t>SICIP required space for 30 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -582,6 +586,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -651,7 +659,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -673,7 +683,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -695,7 +707,9 @@
       <c r="C18" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -717,7 +731,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -739,7 +755,9 @@
       <c r="C20" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -761,7 +779,9 @@
       <c r="C21" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -783,7 +803,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -805,7 +827,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -827,7 +851,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -849,7 +875,9 @@
       <c r="C25" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>3</v>
       </c>
@@ -871,7 +899,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>3</v>
       </c>
@@ -893,7 +923,9 @@
       <c r="C27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>3</v>
       </c>
@@ -915,7 +947,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -937,7 +971,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -959,7 +995,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -981,7 +1019,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>5</v>
       </c>
@@ -1003,7 +1043,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -1025,7 +1067,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -1047,7 +1091,9 @@
       <c r="C34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -1069,7 +1115,9 @@
       <c r="C35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>5</v>
       </c>
@@ -1091,7 +1139,9 @@
       <c r="C36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>3</v>
       </c>
@@ -1237,6 +1287,10 @@
           <t>SICIP required space for 20 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1252,6 +1306,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1321,7 +1379,9 @@
       <c r="C16" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>10</v>
       </c>
@@ -1343,7 +1403,9 @@
       <c r="C17" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>10</v>
       </c>
@@ -1365,7 +1427,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -1387,7 +1451,9 @@
       <c r="C19" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -1409,7 +1475,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -1431,7 +1499,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -1577,6 +1647,10 @@
           <t>SICIP required space for 20 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1592,6 +1666,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1661,7 +1739,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>6</v>
       </c>
@@ -1683,7 +1763,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1705,7 +1787,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -1727,7 +1811,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>4</v>
       </c>
@@ -1749,7 +1835,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>4</v>
       </c>
@@ -1771,7 +1859,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>3</v>
       </c>
@@ -1793,7 +1883,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>10</v>
       </c>
@@ -1815,7 +1907,9 @@
       <c r="C23" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>9</v>
       </c>
@@ -1837,7 +1931,9 @@
       <c r="C24" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -1859,7 +1955,9 @@
       <c r="C25" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -1881,7 +1979,9 @@
       <c r="C26" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>3</v>
       </c>
@@ -2027,6 +2127,10 @@
           <t>SICIP required space for 20 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2042,6 +2146,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2111,7 +2219,9 @@
       <c r="C16" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>10</v>
       </c>
@@ -2133,7 +2243,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>10</v>
       </c>
@@ -2155,7 +2267,9 @@
       <c r="C18" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -2177,7 +2291,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -2199,7 +2315,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -2221,7 +2339,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -2243,7 +2363,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -2265,7 +2387,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -2287,7 +2411,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -2309,7 +2435,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -2455,6 +2583,10 @@
           <t>SICIP required space for 30 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2470,6 +2602,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2539,7 +2675,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2561,7 +2699,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2583,7 +2723,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -2605,7 +2747,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>3</v>
       </c>
@@ -2627,7 +2771,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -2649,7 +2795,9 @@
       <c r="C21" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -2671,7 +2819,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -2693,7 +2843,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -2839,6 +2991,10 @@
           <t>SICIP required space for 20 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2854,6 +3010,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2923,7 +3083,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2945,7 +3107,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2967,7 +3131,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -2989,7 +3155,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>4</v>
       </c>
@@ -3011,7 +3179,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>4</v>
       </c>
@@ -3033,7 +3203,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>3</v>
       </c>
@@ -3055,7 +3227,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -3077,7 +3251,9 @@
       <c r="C23" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>9</v>
       </c>
@@ -3099,7 +3275,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -3245,6 +3423,10 @@
           <t>SICIP required space for 30 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3260,6 +3442,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3329,7 +3515,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -3351,7 +3539,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -3373,7 +3563,9 @@
       <c r="C18" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -3395,7 +3587,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -3417,7 +3611,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -3439,7 +3635,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -3461,7 +3659,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -3483,7 +3683,9 @@
       <c r="C23" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -3505,7 +3707,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -3527,7 +3731,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>7</v>
       </c>
@@ -3549,7 +3755,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -3571,7 +3779,9 @@
       <c r="C27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -3593,7 +3803,9 @@
       <c r="C28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -3615,7 +3827,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>5</v>
       </c>
@@ -3761,6 +3975,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3776,6 +3994,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3845,7 +4067,9 @@
       <c r="C16" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>9</v>
       </c>
@@ -3867,7 +4091,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -3889,7 +4115,9 @@
       <c r="C18" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -3911,7 +4139,9 @@
       <c r="C19" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -3933,7 +4163,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>4</v>
       </c>
@@ -3955,7 +4187,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -3977,7 +4211,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -3999,7 +4235,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -4021,7 +4259,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -4043,7 +4283,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -4065,7 +4307,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -4211,6 +4455,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -4226,6 +4474,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4295,7 +4547,9 @@
       <c r="C16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -4317,7 +4571,9 @@
       <c r="C17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>7</v>
       </c>
@@ -4339,7 +4595,9 @@
       <c r="C18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>7</v>
       </c>
@@ -4361,7 +4619,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -4383,7 +4643,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -4405,7 +4667,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -4427,7 +4691,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -4449,7 +4715,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -4471,7 +4739,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -4493,7 +4763,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -4515,7 +4787,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -4537,7 +4811,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -4559,7 +4835,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -4581,7 +4859,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>3</v>
       </c>
@@ -4603,7 +4883,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>5</v>
       </c>
@@ -4625,7 +4907,9 @@
       <c r="C31" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>8</v>
       </c>
@@ -4647,7 +4931,9 @@
       <c r="C32" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>3</v>
       </c>
@@ -4669,7 +4955,9 @@
       <c r="C33" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -4691,7 +4979,9 @@
       <c r="C34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -4837,6 +5127,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -4851,6 +5145,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4920,7 +5218,9 @@
       <c r="C16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -4942,7 +5242,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -4964,7 +5266,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -4986,7 +5290,9 @@
       <c r="C19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -5008,7 +5314,9 @@
       <c r="C20" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -5030,7 +5338,9 @@
       <c r="C21" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -5052,7 +5362,9 @@
       <c r="C22" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -5074,7 +5386,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -5096,7 +5410,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -5118,7 +5434,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>9</v>
       </c>
@@ -5140,7 +5458,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -5162,7 +5482,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>8</v>
       </c>
@@ -5184,7 +5506,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -5206,7 +5530,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>8</v>
       </c>
@@ -5228,7 +5554,9 @@
       <c r="C30" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -5250,7 +5578,9 @@
       <c r="C31" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -5272,7 +5602,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -5294,7 +5626,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>4</v>
       </c>
@@ -5316,7 +5650,9 @@
       <c r="C34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>7</v>
       </c>
@@ -5462,6 +5798,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -5477,6 +5817,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -5546,7 +5890,9 @@
       <c r="C16" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>6</v>
       </c>
@@ -5568,7 +5914,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -5590,7 +5938,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -5612,7 +5962,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -5634,7 +5986,9 @@
       <c r="C20" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -5656,7 +6010,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -5678,7 +6034,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -5700,7 +6058,9 @@
       <c r="C23" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>4</v>
       </c>
@@ -5722,7 +6082,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -5744,7 +6106,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -5766,7 +6130,9 @@
       <c r="C26" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>3</v>
       </c>
@@ -5788,7 +6154,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -5810,7 +6178,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -5832,7 +6202,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>5</v>
       </c>
@@ -5854,7 +6226,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>5</v>
       </c>
@@ -5923,9 +6297,9 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="A33:G33"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A32:E32"/>
@@ -6000,6 +6374,10 @@
           <t>SICIP required space for 20 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -6014,6 +6392,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -6083,7 +6465,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -6105,7 +6489,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -6127,7 +6513,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>4</v>
       </c>
@@ -6149,7 +6537,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>4</v>
       </c>
@@ -6171,7 +6561,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -6193,7 +6585,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -6215,7 +6609,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -6237,7 +6633,9 @@
       <c r="C23" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -6259,7 +6657,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -6281,7 +6681,9 @@
       <c r="C25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -6303,7 +6705,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -6325,7 +6729,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>

--- a/lab-standards/BGMEA-lab-standard.xlsx
+++ b/lab-standards/BGMEA-lab-standard.xlsx
@@ -3567,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -3591,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -3639,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -3687,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -3711,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -5294,7 +5294,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -5342,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -5366,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -5486,7 +5486,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -5510,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -5534,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -5606,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -5630,7 +5630,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33" s="9">
         <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
@@ -5654,7 +5654,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F34" s="9">
         <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
